--- a/data/uploads/malaria_report.xlsx
+++ b/data/uploads/malaria_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Downloads/MaHIS dataset reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF0B4BA-5B64-7A4A-8AC1-CD01ED295F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527C696A-FD28-A54D-B556-B9F30B5716C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="3200" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
+    <workbookView xWindow="18960" yWindow="760" windowWidth="15600" windowHeight="19400" activeTab="1" xr2:uid="{3D565A06-DCC6-034B-BC7E-69C7A268E9F5}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLE_NAMES" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="143">
   <si>
     <t>name</t>
   </si>
@@ -150,9 +150,6 @@
     <t>concept_name</t>
   </si>
   <si>
-    <t>Primary diagnosis</t>
-  </si>
-  <si>
     <t>obs_value_coded</t>
   </si>
   <si>
@@ -432,15 +429,6 @@
     <t>count_set</t>
   </si>
   <si>
-    <t>Yes | Malaria</t>
-  </si>
-  <si>
-    <t>Yes | Malaria, presumed</t>
-  </si>
-  <si>
-    <t>PREGNANCY STATUS | DIAGNOSIS</t>
-  </si>
-  <si>
     <t>Lumefantrine + Arthemether 1 x 6 |Lumefantrine + Arthemether 2 x 6 | Lumefantrine + Arthemether 3 x 6 |Lumefantrine + Arthemether 4 x 6</t>
   </si>
   <si>
@@ -453,9 +441,6 @@
     <t>Malaria Species | Malaria film</t>
   </si>
   <si>
-    <t>HMIS-Malaria Report</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
@@ -472,6 +457,18 @@
   </si>
   <si>
     <t>REGISTRATION</t>
+  </si>
+  <si>
+    <t>MALARIA HEALTH FACILITY MONTHLY REPORT</t>
+  </si>
+  <si>
+    <t>Yes | Malaria | Malaria</t>
+  </si>
+  <si>
+    <t>Yes | Malaria, presumed | Malaria, presumed</t>
+  </si>
+  <si>
+    <t>Patient pregnant | Primary diagnosis | Secondary diagnosis</t>
   </si>
 </sst>
 </file>
@@ -846,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -881,16 +878,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -898,276 +895,276 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
         <v>48</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
         <v>51</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
         <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
         <v>56</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
         <v>60</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
         <v>64</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>65</v>
-      </c>
-      <c r="D12" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
         <v>71</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
         <v>74</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
         <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
         <v>89</v>
-      </c>
-      <c r="D28" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" t="s">
         <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
         <v>93</v>
-      </c>
-      <c r="D30" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
         <v>95</v>
-      </c>
-      <c r="D31" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1194,10 +1191,10 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -1262,19 +1259,19 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" t="s">
         <v>33</v>
@@ -1283,39 +1280,33 @@
         <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -1324,39 +1315,33 @@
         <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -1365,39 +1350,33 @@
         <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>98</v>
-      </c>
-      <c r="L4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
@@ -1406,936 +1385,930 @@
         <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
-      </c>
-      <c r="L5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F8" t="s">
         <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F9" t="s">
         <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
       </c>
       <c r="G10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" t="s">
         <v>99</v>
       </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" t="s">
-        <v>100</v>
-      </c>
       <c r="K10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
       </c>
       <c r="G11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" t="s">
         <v>99</v>
       </c>
-      <c r="H11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" t="s">
-        <v>97</v>
-      </c>
-      <c r="J11" t="s">
-        <v>100</v>
-      </c>
       <c r="K11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F12" t="s">
         <v>33</v>
       </c>
       <c r="G12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" t="s">
         <v>99</v>
       </c>
-      <c r="H12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" t="s">
-        <v>100</v>
-      </c>
       <c r="K12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F13" t="s">
         <v>33</v>
       </c>
       <c r="G13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" t="s">
         <v>99</v>
       </c>
-      <c r="H13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" t="s">
-        <v>97</v>
-      </c>
-      <c r="J13" t="s">
-        <v>100</v>
-      </c>
       <c r="K13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F14" t="s">
         <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
         <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F15" t="s">
         <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H15" t="s">
         <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F16" t="s">
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
         <v>35</v>
       </c>
       <c r="I16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" t="s">
         <v>102</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>103</v>
       </c>
-      <c r="K16" t="s">
-        <v>104</v>
-      </c>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
         <v>35</v>
       </c>
       <c r="I17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" t="s">
         <v>102</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>103</v>
       </c>
-      <c r="K17" t="s">
-        <v>104</v>
-      </c>
       <c r="L17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H18" t="s">
         <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F19" t="s">
         <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H19" t="s">
         <v>35</v>
       </c>
       <c r="I19" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F20" t="s">
         <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J20" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" t="s">
         <v>103</v>
       </c>
-      <c r="K20" t="s">
-        <v>104</v>
-      </c>
       <c r="L20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F21" t="s">
         <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H21" t="s">
         <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J21" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" t="s">
         <v>103</v>
       </c>
-      <c r="K21" t="s">
-        <v>104</v>
-      </c>
       <c r="L21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F22" t="s">
         <v>33</v>
       </c>
       <c r="G22" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" t="s">
         <v>99</v>
       </c>
-      <c r="H22" t="s">
-        <v>100</v>
-      </c>
       <c r="I22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F23" t="s">
         <v>33</v>
       </c>
       <c r="G23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" t="s">
         <v>99</v>
       </c>
-      <c r="H23" t="s">
-        <v>100</v>
-      </c>
       <c r="I23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F24" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" t="s">
         <v>99</v>
       </c>
-      <c r="H24" t="s">
-        <v>100</v>
-      </c>
       <c r="I24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
       </c>
       <c r="G25" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" t="s">
         <v>99</v>
       </c>
-      <c r="H25" t="s">
-        <v>100</v>
-      </c>
       <c r="I25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
       </c>
       <c r="G26" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" t="s">
         <v>99</v>
       </c>
-      <c r="H26" t="s">
-        <v>100</v>
-      </c>
       <c r="I26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
       </c>
       <c r="G27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" t="s">
         <v>99</v>
       </c>
-      <c r="H27" t="s">
-        <v>100</v>
-      </c>
       <c r="I27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
       </c>
       <c r="G28" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" t="s">
         <v>99</v>
       </c>
-      <c r="H28" t="s">
-        <v>100</v>
-      </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
       </c>
       <c r="G29" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" t="s">
         <v>99</v>
       </c>
-      <c r="H29" t="s">
-        <v>100</v>
-      </c>
       <c r="I29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s">
         <v>33</v>
       </c>
       <c r="G30" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" t="s">
         <v>99</v>
       </c>
-      <c r="H30" t="s">
-        <v>100</v>
-      </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
       </c>
       <c r="G31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H31" t="s">
         <v>99</v>
       </c>
-      <c r="H31" t="s">
-        <v>100</v>
-      </c>
       <c r="I31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
       </c>
       <c r="G32" t="s">
+        <v>98</v>
+      </c>
+      <c r="H32" t="s">
         <v>99</v>
       </c>
-      <c r="H32" t="s">
-        <v>100</v>
-      </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
       </c>
       <c r="G33" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" t="s">
         <v>99</v>
       </c>
-      <c r="H33" t="s">
-        <v>100</v>
-      </c>
       <c r="I33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -2358,7 +2331,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2366,10 +2339,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2384,12 +2357,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2408,10 +2381,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2422,16 +2395,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
